--- a/cadifa_completo_anterior.xlsx
+++ b/cadifa_completo_anterior.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>001.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/cadifa_completo_anterior.xlsx
+++ b/cadifa_completo_anterior.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>001.1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
